--- a/Internship_artifacts/Internship_artifacts/Defect_Tracker Templat.xlsx
+++ b/Internship_artifacts/Internship_artifacts/Defect_Tracker Templat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhik\Downloads\Internship_artifacts\Internship_artifacts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhik\Desktop\Veridict\Internship_artifacts\Internship_artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F22729-C629-4737-8FFC-FF214876D7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BAE817-AD8C-4DB5-9ABD-4B1387BE5B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="103">
   <si>
     <t>Sl No</t>
   </si>
@@ -97,33 +97,18 @@
     <t>Implemented INSUFFICIENT_EVIDENCE handling instead of assigning misleading scores.</t>
   </si>
   <si>
-    <t>Improved evaluation reliability.</t>
-  </si>
-  <si>
     <t>Frontend did not support the new hallucination evaluation status</t>
   </si>
   <si>
     <t>UI</t>
   </si>
   <si>
-    <t>Updated the evaluation dashboard to display "Not Evaluated" for insufficient evidence cases.</t>
-  </si>
-  <si>
-    <t>UI now correctly handles all evaluation outcomes.</t>
-  </si>
-  <si>
     <t>Structured LLM responses occasionally failed schema validation</t>
   </si>
   <si>
     <t>Validation</t>
   </si>
   <si>
-    <t>Strengthened Pydantic validation and standardized JSON output format.</t>
-  </si>
-  <si>
-    <t>No validation issues observed during testing.</t>
-  </si>
-  <si>
     <t>Minor issues identified during end-to-end testing</t>
   </si>
   <si>
@@ -133,7 +118,217 @@
     <t>Fixed identified defects and completed regression testing.</t>
   </si>
   <si>
-    <t>All 67 backend tests passed successfully.</t>
+    <t>Improved evaluation reliability and avoided false hallucination penalties.</t>
+  </si>
+  <si>
+    <t>Updated the evaluation dashboard to display "Not Evaluated" for insufficient-evidence cases.</t>
+  </si>
+  <si>
+    <t>UI now correctly handles insufficient-evidence outcomes.</t>
+  </si>
+  <si>
+    <t>Strengthened Pydantic validation and standardized structured JSON output handling.</t>
+  </si>
+  <si>
+    <t>Structured judge responses validated successfully during testing.</t>
+  </si>
+  <si>
+    <t>Initial Milestone 2 test suite completed successfully.</t>
+  </si>
+  <si>
+    <t>Completeness evaluation required an independent scoring approach</t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
+  </si>
+  <si>
+    <t>Implemented a dedicated Completeness Judge with separate scoring criteria and structured output.</t>
+  </si>
+  <si>
+    <t>Completeness remains independent from Relevance, Accuracy, and Hallucination.</t>
+  </si>
+  <si>
+    <t>Final verdict required consistent combination of multiple judge results</t>
+  </si>
+  <si>
+    <t>Implemented deterministic weighted Verdict scoring using Accuracy, Completeness, Relevance, and Hallucination dimensions.</t>
+  </si>
+  <si>
+    <t>Final score is calculated deterministically rather than relying on another LLM score.</t>
+  </si>
+  <si>
+    <t>Batch CSV files required validation for different input structures</t>
+  </si>
+  <si>
+    <t>Implemented CSV schema validation, required-field checks, optional reference-answer handling, and invalid-row handling.</t>
+  </si>
+  <si>
+    <t>Invalid batch input is rejected before evaluation.</t>
+  </si>
+  <si>
+    <t>Processing every batch row independently caused excessive model calls</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Implemented grouped batch processing so multiple records can be evaluated in fewer Gemini requests.</t>
+  </si>
+  <si>
+    <t>Improved batch efficiency while preserving individual evaluation results.</t>
+  </si>
+  <si>
+    <t>Digital QA PDF input required additional parsing support</t>
+  </si>
+  <si>
+    <t>Extended the batch pipeline to parse structured PDF question-answer data and integrate it with the evaluation workflow.</t>
+  </si>
+  <si>
+    <t>PDF/Digital QA batch workflow verified.</t>
+  </si>
+  <si>
+    <t>Users had limited visibility into long-running batch processing</t>
+  </si>
+  <si>
+    <t>Implemented batch progress tracking with processing status and completion information.</t>
+  </si>
+  <si>
+    <t>Users can monitor batch execution progress.</t>
+  </si>
+  <si>
+    <t>Batch results were difficult to inspect across multiple evaluations</t>
+  </si>
+  <si>
+    <t>Implemented batch statistics, result tables, search, filtering, and evaluation summaries.</t>
+  </si>
+  <si>
+    <t>Batch results are now easier to analyze and review.</t>
+  </si>
+  <si>
+    <t>Batch reports did not initially contain all required evaluation information</t>
+  </si>
+  <si>
+    <t>Reporting</t>
+  </si>
+  <si>
+    <t>Refined batch PDF/CSV reporting to include dimension scores, overall verdicts, and evaluation summaries.</t>
+  </si>
+  <si>
+    <t>Reporting workflow verified with generated output.</t>
+  </si>
+  <si>
+    <t>Dashboard did not initially provide all required Milestone 4 analytics</t>
+  </si>
+  <si>
+    <t>Sprint 3</t>
+  </si>
+  <si>
+    <t>Audited the existing dashboard and implemented analytics for total evaluations, dimension averages, verdict distribution, hallucination statistics, and trends.</t>
+  </si>
+  <si>
+    <t>Dashboard aligned with Milestone 4 scoring requirements.</t>
+  </si>
+  <si>
+    <t>Dashboard needed visual analytics for easier interpretation</t>
+  </si>
+  <si>
+    <t>Added dimension score, verdict distribution, and quality trend visualizations.</t>
+  </si>
+  <si>
+    <t>Charts verified with analytics data.</t>
+  </si>
+  <si>
+    <t>Hallucination analytics initially needed clearer separation of insufficient evidence</t>
+  </si>
+  <si>
+    <t>Separated grounded, hallucinated, and insufficient-evidence populations in the analytics calculations.</t>
+  </si>
+  <si>
+    <t>Insufficient-evidence cases are not incorrectly counted as hallucinations.</t>
+  </si>
+  <si>
+    <t>Analytics required filtering across different evaluation subsets</t>
+  </si>
+  <si>
+    <t>Implemented filters for date range, evaluation mode, verdict, and model metadata where available.</t>
+  </si>
+  <si>
+    <t>Filtered analytics correctly reflect the selected evaluation population.</t>
+  </si>
+  <si>
+    <t>Single evaluation analytics showed missing dimension scores</t>
+  </si>
+  <si>
+    <t>Data Persistence</t>
+  </si>
+  <si>
+    <t>Traced the data flow from judge output through the HistoryMapper and fixed persistence so all individual judge results are stored.</t>
+  </si>
+  <si>
+    <t>Relevance, Accuracy, Hallucination, Completeness, and Verdict results are now preserved for new evaluations.</t>
+  </si>
+  <si>
+    <t>Legacy evaluations contained only summary verdict information</t>
+  </si>
+  <si>
+    <t>Data Integrity</t>
+  </si>
+  <si>
+    <t>Added summary-only handling so missing historical dimension scores are not fabricated or displayed as zero.</t>
+  </si>
+  <si>
+    <t>Legacy records are explicitly treated as summary-only.</t>
+  </si>
+  <si>
+    <t>Batch PDF lacked dedicated hallucination analysis and recommendations</t>
+  </si>
+  <si>
+    <t>Added Hallucination Analysis and Improvement Recommendations sections based on actual batch evaluation results.</t>
+  </si>
+  <si>
+    <t>Final batch PDF contains all required reporting sections.</t>
+  </si>
+  <si>
+    <t>Authentication verification links redirected to localhost during deployment</t>
+  </si>
+  <si>
+    <t>Configuration</t>
+  </si>
+  <si>
+    <t>Updated Supabase Site URL and allowed redirect URLs to use the deployed Vercel frontend.</t>
+  </si>
+  <si>
+    <t>Email verification and OAuth redirects work with the production deployment.</t>
+  </si>
+  <si>
+    <t>Frontend routes returned 404 when refreshed on Vercel</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t>Added SPA rewrite configuration so client-side React routes resolve correctly after refresh.</t>
+  </si>
+  <si>
+    <t>Evaluator, History, and other frontend routes refresh correctly.</t>
+  </si>
+  <si>
+    <t>Uptime monitoring returned 405 for the backend health endpoint</t>
+  </si>
+  <si>
+    <t>Updated the health endpoint to accept both GET and HEAD requests used by monitoring services.</t>
+  </si>
+  <si>
+    <t>UptimeRobot health monitor reports the backend as Up.</t>
+  </si>
+  <si>
+    <t>Final system required complete regression verification across backend and frontend</t>
+  </si>
+  <si>
+    <t>Executed backend tests, frontend build and lint verification, analytics checks, persistence checks, PDF generation, and production workflow tests.</t>
+  </si>
+  <si>
+    <t>Latest documented verification recorded 163 backend tests passed, frontend build passed, lint had 0 errors, and batch PDF generation passed.</t>
   </si>
 </sst>
 </file>
@@ -234,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -245,9 +440,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -264,6 +456,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -569,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="17.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.109375" style="4" bestFit="1" customWidth="1"/>
@@ -579,9 +777,9 @@
     <col min="5" max="5" width="16" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.21875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="41.77734375" style="4" customWidth="1"/>
     <col min="9" max="10" width="21.88671875" style="4" customWidth="1"/>
-    <col min="11" max="11" width="25.44140625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="34.88671875" style="4" customWidth="1"/>
     <col min="12" max="16384" width="17.5546875" style="4"/>
   </cols>
   <sheetData>
@@ -595,401 +793,808 @@
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="F2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="8">
         <v>46210</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="8" t="s">
+      <c r="J2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="8">
         <v>46213</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="J3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <v>46220</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>25</v>
+      <c r="J4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="9">
+      <c r="H5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="8">
         <v>46221</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>29</v>
+      <c r="J5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="9">
+      <c r="F6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="8">
         <v>46222</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
+      <c r="J6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-      <c r="D7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="8" t="s">
+      <c r="D7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="9">
+      <c r="F7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="8">
         <v>46223</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="10" t="s">
+      <c r="J7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
+    <row r="8" spans="1:11" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
+      <c r="D8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="8">
+        <v>46228</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
+      <c r="D9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="8">
+        <v>46230</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
+      <c r="D10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="8">
+        <v>46233</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
+      <c r="D11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="8">
+        <v>46235</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
+      <c r="D12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="8">
+        <v>46236</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+      <c r="D13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="8">
+        <v>46237</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
+      <c r="D14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="8">
+        <v>46239</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
+      <c r="D15" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I15" s="8">
+        <v>46240</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="6"/>
-    </row>
-    <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
+      <c r="D16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="8">
+        <v>46244</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
+      <c r="D17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="8">
+        <v>46246</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
+      <c r="D18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="8">
+        <v>46247</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="55.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
+      <c r="D19" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="8">
+        <v>46249</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="6"/>
+      <c r="D20" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="8">
+        <v>46250</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="12">
+        <v>46250</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" s="12">
+        <v>46251</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="12">
+        <v>46252</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" s="12">
+        <v>46252</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I25" s="12">
+        <v>46252</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I26" s="12">
+        <v>46252</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>102</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>G1:G1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F50FC49184C87E449886FB52439922C9" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f85b7e58c3d8889ba0673e7b34a193a6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b67b99c0-208c-4860-83e0-51466af787c4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d43477c1ade21a66d9a75ba2d5aa042" ns2:_="">
     <xsd:import namespace="b67b99c0-208c-4860-83e0-51466af787c4"/>
@@ -1121,6 +1726,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1131,15 +1742,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{191CB444-B9BF-4C91-94BD-600524521497}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1157,6 +1759,15 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
   <ds:schemaRefs>
